--- a/Excel/Data.xlsx
+++ b/Excel/Data.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -122,6 +122,19 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Employee_Table" displayName="Employee_Table" ref="A1:D1" headerRowCount="1">
+  <autoFilter ref="A1:D1"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="None"/>
+    <tableColumn id="2" name="None"/>
+    <tableColumn id="3" name="None"/>
+    <tableColumn id="4" name="None"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -417,5 +430,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/Excel/Data.xlsx
+++ b/Excel/Data.xlsx
@@ -4,10 +4,11 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Boys" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Girls" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -125,15 +126,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Employee_Table" displayName="Employee_Table" ref="A1:D1" headerRowCount="1">
-  <autoFilter ref="A1:D1"/>
-  <tableColumns count="4">
-    <tableColumn id="1" name="None"/>
-    <tableColumn id="2" name="None"/>
-    <tableColumn id="3" name="None"/>
-    <tableColumn id="4" name="None"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Team_Agnie" displayName="Team_Agnie" ref="A1:C8" headerRowCount="1">
+  <autoFilter ref="A1:C8"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Intial"/>
+    <tableColumn id="2" name="FirstName"/>
+    <tableColumn id="3" name="LastName"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
+  <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
 </table>
 </file>
 
@@ -426,12 +426,199 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Intial</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>FirstName</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>LastName</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sri</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Rengasarathy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Yuvaraj</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Kannan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Naveen</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Raja</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P S</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kiruba</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Nidhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nikish</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>J S</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Prawin</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Kumar</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sethu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Raj</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Intial</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>G R</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Harini</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Prithika</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Excel/Data.xlsx
+++ b/Excel/Data.xlsx
@@ -4,11 +4,12 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Boys" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Girls" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Boys&amp;Girls" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -621,4 +622,190 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Intial</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>FirstName</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>LastName</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sri</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Rengasarathy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Yuvaraj</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Kannan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Naveen</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Raja</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P S</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kiruba</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Nidhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nikish</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>J S</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Prawin</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Kumar</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sethu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Raj</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>G R</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Harini</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Prithika</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Male,Female</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Excel/Data.xlsx
+++ b/Excel/Data.xlsx
@@ -124,6 +124,21 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Sri</author>
+  </authors>
+  <commentList>
+    <comment ref="A12" authorId="0" shapeId="0">
+      <text>
+        <t>This is a Comment.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -630,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,6 +814,9 @@
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -807,5 +825,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>